--- a/data/advanced.xlsx
+++ b/data/advanced.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aheller\Dropbox\CS\3 - Current Projects\TEA-CART again\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://camsys-my.sharepoint.com/personal/slarue_camsys_com/Documents/Documents/idot_github_puller/TEACART/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B619F310-C6DA-4096-873D-880A99A53A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{B619F310-C6DA-4096-873D-880A99A53A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C3E1234-6324-477A-AB1B-DEFE1EFC28DE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{A33ACDFD-014A-4B2F-8FAD-02B00287D07F}"/>
+    <workbookView xWindow="270" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{A33ACDFD-014A-4B2F-8FAD-02B00287D07F}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_forecast" sheetId="1" r:id="rId1"/>
@@ -50,18 +50,6 @@
     <t>Passenger Cars</t>
   </si>
   <si>
-    <t>Light Duty Trucks</t>
-  </si>
-  <si>
-    <t>Medium Duty Trucks</t>
-  </si>
-  <si>
-    <t>Heavy Duty Trucks</t>
-  </si>
-  <si>
-    <t>Light Duty Automobiles</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -156,6 +144,18 @@
   </si>
   <si>
     <t>Energy Source (Diesel/Electric)</t>
+  </si>
+  <si>
+    <t>Light-Duty Trucks</t>
+  </si>
+  <si>
+    <t>Medium-Duty Trucks</t>
+  </si>
+  <si>
+    <t>Heavy-Duty Trucks</t>
+  </si>
+  <si>
+    <t>Light-Duty Automobiles</t>
   </si>
 </sst>
 </file>
@@ -211,9 +211,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -251,7 +251,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -357,7 +357,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -499,7 +499,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -508,16 +508,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50055866-7628-437A-9222-FE6BA120A52B}">
   <dimension ref="A1:AE6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>2021</v>
@@ -610,24 +610,24 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -638,16 +638,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3D26AC-600C-4311-9434-BB36AED01672}">
   <dimension ref="A1:AE7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>2021</v>
@@ -740,29 +740,29 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -773,121 +773,121 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25257236-E1FA-4834-ADF1-B3765F20D5D9}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="5" width="20.140625" customWidth="1"/>
+    <col min="3" max="5" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -901,81 +901,81 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2522103F-ECFF-4805-B93D-4D869DA1F36C}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" customWidth="1"/>
-    <col min="2" max="2" width="33.85546875" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" customWidth="1"/>
+    <col min="2" max="2" width="33.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>198.354755374798</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -986,35 +986,35 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B78C60D9-A139-46A4-8FEC-CDF7BFD9E702}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>6.8639406622490462E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>297.57986556812102</v>
@@ -1028,32 +1028,32 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63FEE0DB-0F72-4444-98D4-482C19D3929A}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="26.28515625" customWidth="1"/>
+    <col min="1" max="2" width="26.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1064,25 +1064,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33CCAFE3-0A10-4A51-A2ED-4041AAB9D655}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="30.85546875" customWidth="1"/>
+    <col min="1" max="2" width="30.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1090,25 +1090,25 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>0.54</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B6">
         <v>0.1</v>
